--- a/packages/calculators/src/modules/test/6.3-leaching-runoff.xlsx
+++ b/packages/calculators/src/modules/test/6.3-leaching-runoff.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10215"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eddiesholl/Code/aginnovationaustralia/emissions-calculators/packages/calculators/src/modules/test/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mackcheesman/Desktop/Work/EAP/Code/emissions-calculators/packages/calculators/src/modules/test/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA1D7434-00C4-A148-9C3C-204CA5CECCE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0169EE45-E4C2-FA45-9C10-ADB8BC14F8E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="51240" yWindow="18000" windowWidth="28800" windowHeight="23520" activeTab="1" xr2:uid="{5678E890-3691-CF46-80E7-00FB1F103661}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15940" activeTab="1" xr2:uid="{5678E890-3691-CF46-80E7-00FB1F103661}"/>
   </bookViews>
   <sheets>
     <sheet name="6.3.1.1 pasture" sheetId="1" r:id="rId1"/>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="103">
   <si>
     <t>Method 1</t>
   </si>
@@ -91,9 +91,6 @@
     <t>Climate zone</t>
   </si>
   <si>
-    <t>Average yield per hectare in kg</t>
-  </si>
-  <si>
     <r>
       <t>𝑀</t>
     </r>
@@ -835,6 +832,18 @@
   </si>
   <si>
     <t>n/a </t>
+  </si>
+  <si>
+    <t>Average yield per hectare in t</t>
+  </si>
+  <si>
+    <t>NOTE: Pending feedback, I think this formula is incorrect. Multiplying by 10^-3 converts the yield in tonnes to gigagrams, not kilograms. I've implemented the </t>
+  </si>
+  <si>
+    <t>Converted to tonnes per hectare here for compatibility with the expected input.</t>
+  </si>
+  <si>
+    <t>Annual production of crop c in kg</t>
   </si>
 </sst>
 </file>
@@ -845,7 +854,7 @@
     <numFmt numFmtId="164" formatCode="0.000"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -895,6 +904,12 @@
       <name val="Helvetica"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Helvetica"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -928,7 +943,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -946,14 +961,11 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1311,34 +1323,39 @@
         <v>0</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:20">
-      <c r="K2" s="1"/>
+      <c r="E2" t="s">
+        <v>101</v>
+      </c>
+      <c r="K2" s="15" t="s">
+        <v>100</v>
+      </c>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
       <c r="N2" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P2" s="1"/>
     </row>
     <row r="3" spans="1:20" ht="34">
       <c r="D3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>99</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G3" s="7"/>
       <c r="H3" s="7"/>
       <c r="I3" s="7"/>
       <c r="J3" s="7"/>
       <c r="K3" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
@@ -1347,49 +1364,49 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" t="s">
         <v>16</v>
       </c>
-      <c r="F4" t="s">
-        <v>17</v>
-      </c>
       <c r="G4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I4" t="s">
         <v>23</v>
       </c>
-      <c r="I4" t="s">
-        <v>24</v>
-      </c>
       <c r="K4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L4" t="s">
+        <v>37</v>
+      </c>
+      <c r="M4" t="s">
         <v>38</v>
       </c>
-      <c r="M4" t="s">
-        <v>39</v>
-      </c>
       <c r="N4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="P4" s="5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="R4" s="6" t="s">
         <v>1</v>
@@ -1397,41 +1414,41 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B5" t="s">
         <v>7</v>
       </c>
       <c r="C5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D5">
         <v>5000</v>
       </c>
       <c r="E5">
-        <f t="shared" ref="E5:E10" si="0">IF(ISBLANK(B5), "", VLOOKUP(C5, $R$20:$W$24,2, FALSE))</f>
-        <v>4.41</v>
+        <f>IF(ISBLANK(B5), "", VLOOKUP(C5, $R$20:$W$24,2, FALSE)/1000)</f>
+        <v>4.4099999999999999E-3</v>
       </c>
       <c r="F5" s="12">
-        <f t="shared" ref="F5:F10" si="1">IF(ISBLANK(B5), "", VLOOKUP(C5, $R$20:$W$24,6, FALSE))</f>
+        <f t="shared" ref="F5:F10" si="0">IF(ISBLANK(B5), "", VLOOKUP(C5, $R$20:$W$24,6, FALSE))</f>
         <v>0.8</v>
       </c>
       <c r="G5" s="12">
-        <f t="shared" ref="G5:G10" si="2">IF(ISBLANK(B5), "", VLOOKUP(C5, $R$20:$W$24,4, FALSE))</f>
+        <f t="shared" ref="G5:G10" si="1">IF(ISBLANK(B5), "", VLOOKUP(C5, $R$20:$W$24,4, FALSE))</f>
         <v>1.4999999999999999E-2</v>
       </c>
       <c r="H5" s="12">
-        <f t="shared" ref="H5:H10" si="3">IF(ISBLANK(B5), "", VLOOKUP(C5, $R$20:$W$24,3, FALSE))</f>
+        <f t="shared" ref="H5:H10" si="2">IF(ISBLANK(B5), "", VLOOKUP(C5, $R$20:$W$24,3, FALSE))</f>
         <v>0.4</v>
       </c>
       <c r="I5" s="12">
-        <f t="shared" ref="I5:I10" si="4">IF(ISBLANK(B5), "", VLOOKUP(C5, $R$20:$W$24,5, FALSE))</f>
+        <f t="shared" ref="I5:I10" si="3">IF(ISBLANK(B5), "", VLOOKUP(C5, $R$20:$W$24,5, FALSE))</f>
         <v>1.2E-2</v>
       </c>
       <c r="J5" s="12"/>
       <c r="K5">
-        <f t="shared" ref="K5:K10" si="5">IF(ISBLANK(B5),"", (D5*(E5/1000) *(1 - F5)*G5)+(D5*(E5/1000)*H5*I5))</f>
-        <v>0.17198999999999998</v>
+        <f>IF(ISBLANK(B5),"", (D5*(E5 * 1000) *(1 - F5)*G5)+(D5*(E5*1000)*H5*I5))</f>
+        <v>171.98999999999998</v>
       </c>
       <c r="L5">
         <f>IF(ISBLANK(A5), "", IF(A5="yes", 1, 0))</f>
@@ -1443,7 +1460,7 @@
       </c>
       <c r="N5">
         <f>K5*L5*M5</f>
-        <v>4.1277599999999991E-2</v>
+        <v>41.277599999999993</v>
       </c>
       <c r="O5">
         <f>IF(ISBLANK(B5),"",$S$8)</f>
@@ -1451,187 +1468,187 @@
       </c>
       <c r="P5">
         <f>IF(ISBLANK(B5), "", N5*O5*$S$10/1000)</f>
-        <v>7.1351279999999977E-7</v>
+        <v>7.1351279999999986E-4</v>
       </c>
     </row>
     <row r="6" spans="1:20">
       <c r="A6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B6" t="s">
         <v>8</v>
       </c>
       <c r="C6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D6">
         <v>50</v>
       </c>
       <c r="E6">
+        <f t="shared" ref="E6:E10" si="4">IF(ISBLANK(B6), "", VLOOKUP(C6, $R$20:$W$24,2, FALSE)/1000)</f>
+        <v>4.4099999999999999E-3</v>
+      </c>
+      <c r="F6" s="12">
         <f t="shared" si="0"/>
-        <v>4.41</v>
-      </c>
-      <c r="F6" s="12">
+        <v>0.8</v>
+      </c>
+      <c r="G6" s="12">
         <f t="shared" si="1"/>
-        <v>0.8</v>
-      </c>
-      <c r="G6" s="12">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="H6" s="12">
         <f t="shared" si="2"/>
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="H6" s="12">
+        <v>0.4</v>
+      </c>
+      <c r="I6" s="12">
         <f t="shared" si="3"/>
-        <v>0.4</v>
-      </c>
-      <c r="I6" s="12">
-        <f t="shared" si="4"/>
         <v>1.2E-2</v>
       </c>
       <c r="J6" s="12"/>
       <c r="K6">
-        <f t="shared" ref="K6:K20" si="6">IF(ISBLANK(B6),"", (D6*(E6/1000) *(1 - F6)*G6)+(D6*(E6/1000)*H6*I6))</f>
-        <v>1.7198999999999999E-3</v>
+        <f t="shared" ref="K6:K10" si="5">IF(ISBLANK(B6),"", (D6*(E6 * 1000) *(1 - F6)*G6)+(D6*(E6*1000)*H6*I6))</f>
+        <v>1.7198999999999998</v>
       </c>
       <c r="L6">
-        <f t="shared" ref="L6:L20" si="7">IF(ISBLANK(A6), "", IF(A6="yes", 1, 0))</f>
+        <f t="shared" ref="L6:L14" si="6">IF(ISBLANK(A6), "", IF(A6="yes", 1, 0))</f>
         <v>0</v>
       </c>
       <c r="M6">
-        <f t="shared" ref="M6:M20" si="8">$S$9</f>
+        <f t="shared" ref="M6:M10" si="7">$S$9</f>
         <v>0.24</v>
       </c>
       <c r="N6">
-        <f t="shared" ref="N6:N20" si="9">K6*L6*M6</f>
+        <f t="shared" ref="N6:N10" si="8">K6*L6*M6</f>
         <v>0</v>
       </c>
       <c r="O6">
-        <f t="shared" ref="O6:O20" si="10">IF(ISBLANK(B6),"",$S$8)</f>
+        <f t="shared" ref="O6:O14" si="9">IF(ISBLANK(B6),"",$S$8)</f>
         <v>1.0999999999999999E-2</v>
       </c>
       <c r="P6">
-        <f t="shared" ref="P6:P20" si="11">IF(ISBLANK(B6), "", N6*O6*$S$10/1000)</f>
+        <f t="shared" ref="P6:P14" si="10">IF(ISBLANK(B6), "", N6*O6*$S$10/1000)</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:20">
       <c r="A7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B7" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D7">
         <v>600</v>
       </c>
       <c r="E7">
+        <f t="shared" si="4"/>
+        <v>8.3400000000000002E-3</v>
+      </c>
+      <c r="F7" s="12">
         <f t="shared" si="0"/>
-        <v>8.34</v>
-      </c>
-      <c r="F7" s="12">
+        <v>0.8</v>
+      </c>
+      <c r="G7" s="12">
         <f t="shared" si="1"/>
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="H7" s="12">
+        <f t="shared" si="2"/>
         <v>0.8</v>
       </c>
-      <c r="G7" s="12">
-        <f t="shared" si="2"/>
-        <v>2.5000000000000001E-2</v>
-      </c>
-      <c r="H7" s="12">
+      <c r="I7" s="12">
         <f t="shared" si="3"/>
-        <v>0.8</v>
-      </c>
-      <c r="I7" s="12">
-        <f t="shared" si="4"/>
         <v>1.6E-2</v>
       </c>
       <c r="J7" s="12"/>
       <c r="K7">
+        <f t="shared" si="5"/>
+        <v>89.071200000000005</v>
+      </c>
+      <c r="L7">
         <f t="shared" si="6"/>
-        <v>8.9071200000000017E-2</v>
-      </c>
-      <c r="L7">
+        <v>1</v>
+      </c>
+      <c r="M7">
         <f t="shared" si="7"/>
-        <v>1</v>
-      </c>
-      <c r="M7">
+        <v>0.24</v>
+      </c>
+      <c r="N7">
         <f t="shared" si="8"/>
-        <v>0.24</v>
-      </c>
-      <c r="N7">
+        <v>21.377088000000001</v>
+      </c>
+      <c r="O7">
         <f t="shared" si="9"/>
-        <v>2.1377088000000002E-2</v>
-      </c>
-      <c r="O7">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="P7">
         <f t="shared" si="10"/>
-        <v>1.0999999999999999E-2</v>
-      </c>
-      <c r="P7">
-        <f t="shared" si="11"/>
-        <v>3.6951823542857145E-7</v>
+        <v>3.6951823542857138E-4</v>
       </c>
     </row>
     <row r="8" spans="1:20">
       <c r="A8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B8" t="s">
         <v>8</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D8">
         <v>7000</v>
       </c>
       <c r="E8">
+        <f t="shared" si="4"/>
+        <v>8.6199999999999992E-3</v>
+      </c>
+      <c r="F8" s="12">
         <f t="shared" si="0"/>
-        <v>8.6199999999999992</v>
-      </c>
-      <c r="F8" s="12">
+        <v>0.8</v>
+      </c>
+      <c r="G8" s="12">
         <f t="shared" si="1"/>
-        <v>0.8</v>
-      </c>
-      <c r="G8" s="12">
+        <v>2.7E-2</v>
+      </c>
+      <c r="H8" s="12">
         <f t="shared" si="2"/>
-        <v>2.7E-2</v>
-      </c>
-      <c r="H8" s="12">
+        <v>0.4</v>
+      </c>
+      <c r="I8" s="12">
         <f t="shared" si="3"/>
-        <v>0.4</v>
-      </c>
-      <c r="I8" s="12">
-        <f t="shared" si="4"/>
         <v>1.9E-2</v>
       </c>
       <c r="J8" s="12"/>
       <c r="K8">
+        <f t="shared" si="5"/>
+        <v>784.41999999999985</v>
+      </c>
+      <c r="L8">
         <f t="shared" si="6"/>
-        <v>0.7844199999999999</v>
-      </c>
-      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
         <f t="shared" si="7"/>
+        <v>0.24</v>
+      </c>
+      <c r="N8">
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="M8">
-        <f t="shared" si="8"/>
-        <v>0.24</v>
-      </c>
-      <c r="N8">
+      <c r="O8">
         <f t="shared" si="9"/>
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="P8">
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="O8">
-        <f t="shared" si="10"/>
-        <v>1.0999999999999999E-2</v>
-      </c>
-      <c r="P8">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
       <c r="R8" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="S8" s="2">
         <v>1.0999999999999999E-2</v>
@@ -1639,64 +1656,64 @@
     </row>
     <row r="9" spans="1:20">
       <c r="A9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B9" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D9">
         <v>50</v>
       </c>
       <c r="E9">
+        <f t="shared" si="4"/>
+        <v>5.62E-3</v>
+      </c>
+      <c r="F9" s="12">
         <f t="shared" si="0"/>
-        <v>5.62</v>
-      </c>
-      <c r="F9" s="12">
+        <v>0.8</v>
+      </c>
+      <c r="G9" s="12">
         <f t="shared" si="1"/>
-        <v>0.8</v>
-      </c>
-      <c r="G9" s="12">
+        <v>2.7E-2</v>
+      </c>
+      <c r="H9" s="12">
         <f t="shared" si="2"/>
-        <v>2.7E-2</v>
-      </c>
-      <c r="H9" s="12">
+        <v>0.4</v>
+      </c>
+      <c r="I9" s="12">
         <f t="shared" si="3"/>
-        <v>0.4</v>
-      </c>
-      <c r="I9" s="12">
-        <f t="shared" si="4"/>
         <v>2.1999999999999999E-2</v>
       </c>
       <c r="J9" s="12"/>
       <c r="K9">
+        <f t="shared" si="5"/>
+        <v>3.9901999999999997</v>
+      </c>
+      <c r="L9">
         <f t="shared" si="6"/>
-        <v>3.9902000000000002E-3</v>
-      </c>
-      <c r="L9">
+        <v>1</v>
+      </c>
+      <c r="M9">
         <f t="shared" si="7"/>
-        <v>1</v>
-      </c>
-      <c r="M9">
+        <v>0.24</v>
+      </c>
+      <c r="N9">
         <f t="shared" si="8"/>
-        <v>0.24</v>
-      </c>
-      <c r="N9">
+        <v>0.95764799999999994</v>
+      </c>
+      <c r="O9">
         <f t="shared" si="9"/>
-        <v>9.5764799999999996E-4</v>
-      </c>
-      <c r="O9">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="P9">
         <f t="shared" si="10"/>
-        <v>1.0999999999999999E-2</v>
-      </c>
-      <c r="P9">
-        <f t="shared" si="11"/>
-        <v>1.6553629714285714E-8</v>
+        <v>1.655362971428571E-5</v>
       </c>
       <c r="R9" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="S9" s="2">
         <v>0.24</v>
@@ -1704,60 +1721,60 @@
     </row>
     <row r="10" spans="1:20">
       <c r="A10" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B10" t="s">
         <v>8</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D10">
         <v>50</v>
       </c>
       <c r="E10">
+        <f t="shared" si="4"/>
+        <v>8.3499999999999998E-3</v>
+      </c>
+      <c r="F10" s="12">
         <f t="shared" si="0"/>
-        <v>8.35</v>
-      </c>
-      <c r="F10" s="12">
+        <v>0.8</v>
+      </c>
+      <c r="G10" s="12">
         <f t="shared" si="1"/>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="H10" s="12">
+        <f t="shared" si="2"/>
         <v>0.8</v>
       </c>
-      <c r="G10" s="12">
-        <f t="shared" si="2"/>
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="H10" s="12">
+      <c r="I10" s="12">
         <f t="shared" si="3"/>
-        <v>0.8</v>
-      </c>
-      <c r="I10" s="12">
-        <f t="shared" si="4"/>
         <v>1.2E-2</v>
       </c>
       <c r="J10" s="12"/>
       <c r="K10">
+        <f t="shared" si="5"/>
+        <v>5.2604999999999995</v>
+      </c>
+      <c r="L10">
         <f t="shared" si="6"/>
-        <v>5.2604999999999996E-3</v>
-      </c>
-      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
         <f t="shared" si="7"/>
+        <v>0.24</v>
+      </c>
+      <c r="N10">
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="M10">
-        <f t="shared" si="8"/>
-        <v>0.24</v>
-      </c>
-      <c r="N10">
+      <c r="O10">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="O10">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="P10">
         <f t="shared" si="10"/>
-        <v>1.0999999999999999E-2</v>
-      </c>
-      <c r="P10">
-        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="R10" t="s">
@@ -1770,36 +1787,36 @@
     </row>
     <row r="11" spans="1:20">
       <c r="F11" s="12" t="str">
-        <f t="shared" ref="F11:F20" si="12">IF(ISBLANK(B11), "", VLOOKUP(C11, $R$20:$W$24,6, FALSE))</f>
+        <f t="shared" ref="F11:F14" si="11">IF(ISBLANK(B11), "", VLOOKUP(C11, $R$20:$W$24,6, FALSE))</f>
         <v/>
       </c>
       <c r="G11" s="12" t="str">
-        <f t="shared" ref="G11:G20" si="13">IF(ISBLANK(B11), "", VLOOKUP(C11, $R$20:$W$24,4, FALSE))</f>
+        <f t="shared" ref="G11:G14" si="12">IF(ISBLANK(B11), "", VLOOKUP(C11, $R$20:$W$24,4, FALSE))</f>
         <v/>
       </c>
       <c r="H11" s="12" t="str">
-        <f t="shared" ref="H11:H20" si="14">IF(ISBLANK(B11), "", VLOOKUP(C11, $R$20:$W$24,3, FALSE))</f>
+        <f t="shared" ref="H11:H14" si="13">IF(ISBLANK(B11), "", VLOOKUP(C11, $R$20:$W$24,3, FALSE))</f>
         <v/>
       </c>
       <c r="I11" s="12" t="str">
-        <f t="shared" ref="I11:I20" si="15">IF(ISBLANK(B11), "", VLOOKUP(C11, $R$20:$W$24,5, FALSE))</f>
+        <f t="shared" ref="I11:I14" si="14">IF(ISBLANK(B11), "", VLOOKUP(C11, $R$20:$W$24,5, FALSE))</f>
         <v/>
       </c>
       <c r="J11" s="12"/>
       <c r="K11" t="str">
+        <f t="shared" ref="K6:K14" si="15">IF(ISBLANK(B11),"", (D11*(E11/1000) *(1 - F11)*G11)+(D11*(E11/1000)*H11*I11))</f>
+        <v/>
+      </c>
+      <c r="L11" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="L11" t="str">
-        <f t="shared" si="7"/>
+      <c r="O11" t="str">
+        <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="O11" t="str">
+      <c r="P11" t="str">
         <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="P11" t="str">
-        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R11" s="2"/>
@@ -1812,36 +1829,36 @@
         <v/>
       </c>
       <c r="F12" s="12" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G12" s="12" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="G12" s="12" t="str">
+      <c r="H12" s="12" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="H12" s="12" t="str">
+      <c r="I12" s="12" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="I12" s="12" t="str">
+      <c r="J12" s="12"/>
+      <c r="K12" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="J12" s="12"/>
-      <c r="K12" t="str">
+      <c r="L12" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="L12" t="str">
-        <f t="shared" si="7"/>
+      <c r="O12" t="str">
+        <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="O12" t="str">
+      <c r="P12" t="str">
         <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="P12" t="str">
-        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R12" s="2" t="s">
@@ -1856,36 +1873,36 @@
         <v/>
       </c>
       <c r="F13" s="12" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G13" s="12" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="G13" s="12" t="str">
+      <c r="H13" s="12" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="H13" s="12" t="str">
+      <c r="I13" s="12" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="I13" s="12" t="str">
+      <c r="J13" s="12"/>
+      <c r="K13" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="J13" s="12"/>
-      <c r="K13" t="str">
+      <c r="L13" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="L13" t="str">
-        <f t="shared" si="7"/>
+      <c r="O13" t="str">
+        <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="O13" t="str">
+      <c r="P13" t="str">
         <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="P13" t="str">
-        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R13" t="s">
@@ -1899,36 +1916,36 @@
         <v/>
       </c>
       <c r="F14" s="12" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G14" s="12" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="G14" s="12" t="str">
+      <c r="H14" s="12" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="H14" s="12" t="str">
+      <c r="I14" s="12" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="I14" s="12" t="str">
+      <c r="J14" s="12"/>
+      <c r="K14" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="J14" s="12"/>
-      <c r="K14" t="str">
+      <c r="L14" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="L14" t="str">
-        <f t="shared" si="7"/>
+      <c r="O14" t="str">
+        <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="O14" t="str">
+      <c r="P14" t="str">
         <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="P14" t="str">
-        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R14" s="2" t="s">
@@ -1960,7 +1977,6 @@
     </row>
     <row r="16" spans="1:20">
       <c r="C16" s="2"/>
-      <c r="E16" s="13"/>
       <c r="F16" s="12"/>
       <c r="G16" s="12"/>
       <c r="H16" s="12"/>
@@ -1971,7 +1987,6 @@
       <c r="T16" s="8"/>
     </row>
     <row r="17" spans="3:26">
-      <c r="E17" s="13"/>
       <c r="F17" s="12"/>
       <c r="G17" s="12"/>
       <c r="H17" s="12"/>
@@ -1980,7 +1995,6 @@
     </row>
     <row r="18" spans="3:26">
       <c r="C18" s="2"/>
-      <c r="E18" s="13"/>
       <c r="F18" s="12"/>
       <c r="G18" s="12"/>
       <c r="H18" s="12"/>
@@ -1991,41 +2005,39 @@
     </row>
     <row r="19" spans="3:26" ht="17">
       <c r="C19" s="2"/>
-      <c r="E19" s="13"/>
       <c r="F19" s="12"/>
       <c r="G19" s="12"/>
       <c r="H19" s="12"/>
       <c r="I19" s="12"/>
       <c r="J19" s="12"/>
       <c r="R19" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="S19" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="T19" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="S19" s="2" t="s">
+      <c r="U19" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="V19" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="W19" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="T19" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="U19" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="V19" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="W19" s="2" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="20" spans="3:26">
       <c r="C20" s="2"/>
-      <c r="E20" s="13"/>
       <c r="F20" s="12"/>
       <c r="G20" s="12"/>
       <c r="H20" s="12"/>
       <c r="I20" s="12"/>
       <c r="J20" s="12"/>
       <c r="R20" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="S20" s="2">
         <v>4.41</v>
@@ -2045,7 +2057,7 @@
     </row>
     <row r="21" spans="3:26">
       <c r="R21" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="S21" s="2">
         <v>8.34</v>
@@ -2065,7 +2077,7 @@
     </row>
     <row r="22" spans="3:26">
       <c r="R22" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="S22" s="2">
         <v>8.6199999999999992</v>
@@ -2089,7 +2101,7 @@
     <row r="23" spans="3:26">
       <c r="C23" s="2"/>
       <c r="R23" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="S23" s="2">
         <v>5.62</v>
@@ -2113,7 +2125,7 @@
     <row r="24" spans="3:26">
       <c r="C24" s="2"/>
       <c r="R24" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S24" s="2">
         <v>8.35</v>
@@ -2393,7 +2405,7 @@
         <v>0</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:26">
@@ -2402,36 +2414,38 @@
       <c r="R2" s="1"/>
       <c r="S2" s="1"/>
       <c r="T2" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="V2" s="1"/>
     </row>
-    <row r="3" spans="1:26" ht="51">
+    <row r="3" spans="1:26" ht="68">
       <c r="B3" s="3"/>
       <c r="G3" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="H3" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="I3" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="J3" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="I3" s="7"/>
-      <c r="J3" s="7" t="s">
+      <c r="K3" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="K3" s="7" t="s">
+      <c r="L3" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="L3" s="7" t="s">
+      <c r="M3" s="7" t="s">
         <v>44</v>
-      </c>
-      <c r="M3" s="7" t="s">
-        <v>45</v>
       </c>
       <c r="N3" s="7"/>
       <c r="O3" s="7"/>
       <c r="P3" s="7"/>
       <c r="Q3" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="R3" s="1"/>
       <c r="S3" s="1"/>
@@ -2440,64 +2454,64 @@
     </row>
     <row r="4" spans="1:26" ht="34">
       <c r="A4" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="B4" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="B4" s="13" t="s">
         <v>9</v>
       </c>
       <c r="C4" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D4" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="E4" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="F4" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G4" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="F4" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4" s="4" t="s">
+      <c r="H4" t="s">
         <v>50</v>
       </c>
-      <c r="H4" t="s">
+      <c r="I4" t="s">
         <v>51</v>
       </c>
-      <c r="I4" t="s">
+      <c r="J4" t="s">
         <v>52</v>
       </c>
-      <c r="J4" t="s">
+      <c r="K4" t="s">
         <v>53</v>
       </c>
-      <c r="K4" t="s">
+      <c r="L4" t="s">
         <v>54</v>
       </c>
-      <c r="L4" t="s">
+      <c r="M4" t="s">
         <v>55</v>
       </c>
-      <c r="M4" t="s">
+      <c r="O4" t="s">
         <v>56</v>
       </c>
-      <c r="O4" t="s">
+      <c r="Q4" t="s">
         <v>57</v>
       </c>
-      <c r="Q4" t="s">
+      <c r="R4" t="s">
+        <v>37</v>
+      </c>
+      <c r="S4" t="s">
+        <v>38</v>
+      </c>
+      <c r="T4" t="s">
+        <v>32</v>
+      </c>
+      <c r="U4" t="s">
+        <v>31</v>
+      </c>
+      <c r="V4" s="5" t="s">
         <v>58</v>
-      </c>
-      <c r="R4" t="s">
-        <v>38</v>
-      </c>
-      <c r="S4" t="s">
-        <v>39</v>
-      </c>
-      <c r="T4" t="s">
-        <v>33</v>
-      </c>
-      <c r="U4" t="s">
-        <v>32</v>
-      </c>
-      <c r="V4" s="5" t="s">
-        <v>59</v>
       </c>
       <c r="X4" s="6" t="s">
         <v>1</v>
@@ -2505,22 +2519,22 @@
     </row>
     <row r="5" spans="1:26">
       <c r="A5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C5" t="s">
+        <v>59</v>
+      </c>
+      <c r="D5" t="s">
         <v>60</v>
-      </c>
-      <c r="D5" t="s">
-        <v>61</v>
       </c>
       <c r="E5">
         <v>50</v>
       </c>
       <c r="F5">
-        <v>2000</v>
+        <v>2</v>
       </c>
       <c r="G5" s="12">
         <v>0.2</v>
@@ -2530,23 +2544,23 @@
         <v>0</v>
       </c>
       <c r="I5" s="12">
-        <f t="shared" ref="I5:I14" si="0">IF(ISBLANK(B5), "", E5*F5)</f>
+        <f>IF(ISBLANK(B5), "", E5*(F5*1000))</f>
         <v>100000</v>
       </c>
       <c r="J5" s="12">
-        <f t="shared" ref="J5:J14" si="1">IF(ISBLANK($B5), "", VLOOKUP($C5, $X$22:$AF$39, 2, FALSE))</f>
+        <f t="shared" ref="J5:J14" si="0">IF(ISBLANK($B5), "", VLOOKUP($C5, $X$22:$AF$39, 2, FALSE))</f>
         <v>0.25</v>
       </c>
       <c r="K5" s="12">
-        <f t="shared" ref="K5:K14" si="2">IF(ISBLANK($B5), "", VLOOKUP($C5, $X$22:$AF$39, 3, FALSE))</f>
+        <f t="shared" ref="K5:K14" si="1">IF(ISBLANK($B5), "", VLOOKUP($C5, $X$22:$AF$39, 3, FALSE))</f>
         <v>0.45</v>
       </c>
       <c r="L5" s="12">
-        <f t="shared" ref="L5:L14" si="3">IF(ISBLANK($B5), "", VLOOKUP($C5, $X$22:$AF$39, 4, FALSE))</f>
+        <f t="shared" ref="L5:L14" si="2">IF(ISBLANK($B5), "", VLOOKUP($C5, $X$22:$AF$39, 4, FALSE))</f>
         <v>0.2</v>
       </c>
       <c r="M5" s="12">
-        <f t="shared" ref="M5:M14" si="4">IF(ISBLANK($B5), "", VLOOKUP($C5, $X$22:$AF$39, 6, FALSE))</f>
+        <f t="shared" ref="M5:M14" si="3">IF(ISBLANK($B5), "", VLOOKUP($C5, $X$22:$AF$39, 6, FALSE))</f>
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="N5" s="12">
@@ -2554,7 +2568,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="O5" s="12">
-        <f t="shared" ref="O5:O14" si="5">IF(ISBLANK($B5), "", VLOOKUP($C5, $X$22:$AF$39, 7, FALSE))</f>
+        <f t="shared" ref="O5:O14" si="4">IF(ISBLANK($B5), "", VLOOKUP($C5, $X$22:$AF$39, 7, FALSE))</f>
         <v>7.0000000000000001E-3</v>
       </c>
       <c r="P5" s="12">
@@ -2562,7 +2576,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
       <c r="Q5">
-        <f t="shared" ref="Q5:Q14" si="6">IF(ISBLANK(B5),"", (I5*J5*(1 - G5 - H5) * L5*N5)+(I5*J5*K5*L5*P5))</f>
+        <f t="shared" ref="Q5:Q14" si="5">IF(ISBLANK(B5),"", (I5*J5*(1 - G5 - H5) * L5*N5)+(I5*J5*K5*L5*P5))</f>
         <v>35.75</v>
       </c>
       <c r="R5">
@@ -2588,22 +2602,22 @@
     </row>
     <row r="6" spans="1:26">
       <c r="A6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C6" t="s">
+        <v>59</v>
+      </c>
+      <c r="D6" t="s">
         <v>60</v>
-      </c>
-      <c r="D6" t="s">
-        <v>61</v>
       </c>
       <c r="E6">
         <v>50</v>
       </c>
       <c r="F6">
-        <v>2000</v>
+        <v>2</v>
       </c>
       <c r="G6">
         <v>0.2</v>
@@ -2612,24 +2626,24 @@
         <f t="array" ref="H6">_xlfn.IFS(ISBLANK(B6), "",C6="Sugar Cane", VLOOKUP(D6, $Y$48:$Z$50, 2, FALSE),_xlfn.IFNA(MATCH(C6, $X$43:$X$47, 0), FALSE), VLOOKUP(C6, $X$43:$Z$47, 3, FALSE), TRUE, VLOOKUP(D6, $Y$51:$Z$53, 2, FALSE))</f>
         <v>0</v>
       </c>
-      <c r="I6">
+      <c r="I6" s="12">
+        <f t="shared" ref="I6:I14" si="6">IF(ISBLANK(B6), "", E6*(F6*1000))</f>
+        <v>100000</v>
+      </c>
+      <c r="J6" s="12">
         <f t="shared" si="0"/>
-        <v>100000</v>
-      </c>
-      <c r="J6" s="12">
+        <v>0.25</v>
+      </c>
+      <c r="K6" s="12">
         <f t="shared" si="1"/>
-        <v>0.25</v>
-      </c>
-      <c r="K6" s="12">
+        <v>0.45</v>
+      </c>
+      <c r="L6" s="12">
         <f t="shared" si="2"/>
-        <v>0.45</v>
-      </c>
-      <c r="L6" s="12">
+        <v>0.2</v>
+      </c>
+      <c r="M6" s="12">
         <f t="shared" si="3"/>
-        <v>0.2</v>
-      </c>
-      <c r="M6" s="12">
-        <f t="shared" si="4"/>
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="N6" s="12">
@@ -2637,7 +2651,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="O6" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>7.0000000000000001E-3</v>
       </c>
       <c r="P6">
@@ -2645,7 +2659,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
       <c r="Q6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>35.75</v>
       </c>
       <c r="R6">
@@ -2671,22 +2685,22 @@
     </row>
     <row r="7" spans="1:26">
       <c r="A7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E7">
         <v>50</v>
       </c>
       <c r="F7">
-        <v>2000</v>
+        <v>2</v>
       </c>
       <c r="G7">
         <v>0.2</v>
@@ -2695,24 +2709,24 @@
         <f t="array" ref="H7">_xlfn.IFS(ISBLANK(B7), "",C7="Sugar Cane", VLOOKUP(D7, $Y$48:$Z$50, 2, FALSE),_xlfn.IFNA(MATCH(C7, $X$43:$X$47, 0), FALSE), VLOOKUP(C7, $X$43:$Z$47, 3, FALSE), TRUE, VLOOKUP(D7, $Y$51:$Z$53, 2, FALSE))</f>
         <v>0.06</v>
       </c>
-      <c r="I7">
+      <c r="I7" s="12">
+        <f t="shared" si="6"/>
+        <v>100000</v>
+      </c>
+      <c r="J7" s="12">
         <f t="shared" si="0"/>
-        <v>100000</v>
-      </c>
-      <c r="J7" s="12">
+        <v>1.31</v>
+      </c>
+      <c r="K7" s="12">
         <f t="shared" si="1"/>
-        <v>1.31</v>
-      </c>
-      <c r="K7" s="12">
+        <v>0.16</v>
+      </c>
+      <c r="L7" s="12">
         <f t="shared" si="2"/>
-        <v>0.16</v>
-      </c>
-      <c r="L7" s="12">
+        <v>0.8</v>
+      </c>
+      <c r="M7" s="12">
         <f t="shared" si="3"/>
-        <v>0.8</v>
-      </c>
-      <c r="M7" s="12">
-        <f t="shared" si="4"/>
         <v>7.0000000000000001E-3</v>
       </c>
       <c r="N7" s="12">
@@ -2720,7 +2734,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
       <c r="O7" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0.01</v>
       </c>
       <c r="P7">
@@ -2728,7 +2742,7 @@
         <v>0.01</v>
       </c>
       <c r="Q7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>710.5440000000001</v>
       </c>
       <c r="R7">
@@ -2754,22 +2768,22 @@
     </row>
     <row r="8" spans="1:26">
       <c r="A8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>62</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>63</v>
       </c>
       <c r="E8">
         <v>50</v>
       </c>
       <c r="F8">
-        <v>2000</v>
+        <v>2</v>
       </c>
       <c r="G8">
         <v>0.2</v>
@@ -2778,24 +2792,24 @@
         <f t="array" ref="H8">_xlfn.IFS(ISBLANK(B8), "",C8="Sugar Cane", VLOOKUP(D8, $Y$48:$Z$50, 2, FALSE),_xlfn.IFNA(MATCH(C8, $X$43:$X$47, 0), FALSE), VLOOKUP(C8, $X$43:$Z$47, 3, FALSE), TRUE, VLOOKUP(D8, $Y$51:$Z$53, 2, FALSE))</f>
         <v>0.06</v>
       </c>
-      <c r="I8">
+      <c r="I8" s="12">
+        <f t="shared" si="6"/>
+        <v>100000</v>
+      </c>
+      <c r="J8" s="12">
         <f t="shared" si="0"/>
-        <v>100000</v>
-      </c>
-      <c r="J8" s="12">
+        <v>1.31</v>
+      </c>
+      <c r="K8" s="12">
         <f t="shared" si="1"/>
-        <v>1.31</v>
-      </c>
-      <c r="K8" s="12">
+        <v>0.16</v>
+      </c>
+      <c r="L8" s="12">
         <f t="shared" si="2"/>
-        <v>0.16</v>
-      </c>
-      <c r="L8" s="12">
+        <v>0.8</v>
+      </c>
+      <c r="M8" s="12">
         <f t="shared" si="3"/>
-        <v>0.8</v>
-      </c>
-      <c r="M8" s="12">
-        <f t="shared" si="4"/>
         <v>7.0000000000000001E-3</v>
       </c>
       <c r="N8" s="12">
@@ -2803,7 +2817,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
       <c r="O8" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0.01</v>
       </c>
       <c r="P8">
@@ -2811,7 +2825,7 @@
         <v>0.01</v>
       </c>
       <c r="Q8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>710.5440000000001</v>
       </c>
       <c r="R8">
@@ -2835,7 +2849,7 @@
         <v>0</v>
       </c>
       <c r="X8" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="Y8" s="2">
         <v>1.0999999999999999E-2</v>
@@ -2843,22 +2857,22 @@
     </row>
     <row r="9" spans="1:26">
       <c r="A9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>64</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>65</v>
       </c>
       <c r="E9">
         <v>50</v>
       </c>
       <c r="F9">
-        <v>2000</v>
+        <v>2</v>
       </c>
       <c r="G9">
         <v>0.2</v>
@@ -2867,24 +2881,24 @@
         <f t="array" ref="H9">_xlfn.IFS(ISBLANK(B9), "",C9="Sugar Cane", VLOOKUP(D9, $Y$48:$Z$50, 2, FALSE),_xlfn.IFNA(MATCH(C9, $X$43:$X$47, 0), FALSE), VLOOKUP(C9, $X$43:$Z$47, 3, FALSE), TRUE, VLOOKUP(D9, $Y$51:$Z$53, 2, FALSE))</f>
         <v>1</v>
       </c>
-      <c r="I9">
+      <c r="I9" s="12">
+        <f t="shared" si="6"/>
+        <v>100000</v>
+      </c>
+      <c r="J9" s="12">
         <f t="shared" si="0"/>
-        <v>100000</v>
-      </c>
-      <c r="J9" s="12">
+        <v>0.34</v>
+      </c>
+      <c r="K9" s="12">
         <f t="shared" si="1"/>
-        <v>0.34</v>
-      </c>
-      <c r="K9" s="12">
+        <v>0.43</v>
+      </c>
+      <c r="L9" s="12">
         <f t="shared" si="2"/>
-        <v>0.43</v>
-      </c>
-      <c r="L9" s="12">
+        <v>0.25</v>
+      </c>
+      <c r="M9" s="12">
         <f t="shared" si="3"/>
-        <v>0.25</v>
-      </c>
-      <c r="M9" s="12">
-        <f t="shared" si="4"/>
         <v>0.02</v>
       </c>
       <c r="N9" s="12">
@@ -2892,7 +2906,7 @@
         <v>0.02</v>
       </c>
       <c r="O9" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0.01</v>
       </c>
       <c r="P9">
@@ -2900,7 +2914,7 @@
         <v>0.01</v>
       </c>
       <c r="Q9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>2.5500000000000114</v>
       </c>
       <c r="R9">
@@ -2924,7 +2938,7 @@
         <v>1.0578857142857189E-5</v>
       </c>
       <c r="X9" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="Y9" s="2">
         <v>0.24</v>
@@ -2932,22 +2946,22 @@
     </row>
     <row r="10" spans="1:26">
       <c r="A10" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E10">
         <v>50</v>
       </c>
       <c r="F10">
-        <v>2000</v>
+        <v>2</v>
       </c>
       <c r="G10">
         <v>0.3</v>
@@ -2956,24 +2970,24 @@
         <f t="array" ref="H10">_xlfn.IFS(ISBLANK(B10), "",C10="Sugar Cane", VLOOKUP(D10, $Y$48:$Z$50, 2, FALSE),_xlfn.IFNA(MATCH(C10, $X$43:$X$47, 0), FALSE), VLOOKUP(C10, $X$43:$Z$47, 3, FALSE), TRUE, VLOOKUP(D10, $Y$51:$Z$53, 2, FALSE))</f>
         <v>1</v>
       </c>
-      <c r="I10">
+      <c r="I10" s="12">
+        <f t="shared" si="6"/>
+        <v>100000</v>
+      </c>
+      <c r="J10" s="12">
         <f t="shared" si="0"/>
-        <v>100000</v>
-      </c>
-      <c r="J10" s="12">
+        <v>0.34</v>
+      </c>
+      <c r="K10" s="12">
         <f t="shared" si="1"/>
-        <v>0.34</v>
-      </c>
-      <c r="K10" s="12">
+        <v>0.43</v>
+      </c>
+      <c r="L10" s="12">
         <f t="shared" si="2"/>
-        <v>0.43</v>
-      </c>
-      <c r="L10" s="12">
+        <v>0.25</v>
+      </c>
+      <c r="M10" s="12">
         <f t="shared" si="3"/>
-        <v>0.25</v>
-      </c>
-      <c r="M10" s="12">
-        <f t="shared" si="4"/>
         <v>0.02</v>
       </c>
       <c r="N10" s="12">
@@ -2981,7 +2995,7 @@
         <v>0.02</v>
       </c>
       <c r="O10" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0.01</v>
       </c>
       <c r="P10">
@@ -2989,7 +3003,7 @@
         <v>0.01</v>
       </c>
       <c r="Q10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>-14.450000000000003</v>
       </c>
       <c r="R10">
@@ -3022,22 +3036,22 @@
     </row>
     <row r="11" spans="1:26">
       <c r="A11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>67</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>68</v>
       </c>
       <c r="E11">
         <v>50</v>
       </c>
       <c r="F11">
-        <v>2000</v>
+        <v>2</v>
       </c>
       <c r="G11">
         <v>0.3</v>
@@ -3046,24 +3060,24 @@
         <f t="array" ref="H11">_xlfn.IFS(ISBLANK(B11), "",C11="Sugar Cane", VLOOKUP(D11, $Y$48:$Z$50, 2, FALSE),_xlfn.IFNA(MATCH(C11, $X$43:$X$47, 0), FALSE), VLOOKUP(C11, $X$43:$Z$47, 3, FALSE), TRUE, VLOOKUP(D11, $Y$51:$Z$53, 2, FALSE))</f>
         <v>0</v>
       </c>
-      <c r="I11">
+      <c r="I11" s="12">
+        <f t="shared" si="6"/>
+        <v>100000</v>
+      </c>
+      <c r="J11" s="12">
         <f t="shared" si="0"/>
-        <v>100000</v>
-      </c>
-      <c r="J11" s="12">
+        <v>1.9</v>
+      </c>
+      <c r="K11" s="12">
         <f t="shared" si="1"/>
-        <v>1.9</v>
-      </c>
-      <c r="K11" s="12">
+        <v>0.3</v>
+      </c>
+      <c r="L11" s="12">
         <f t="shared" si="2"/>
-        <v>0.3</v>
-      </c>
-      <c r="L11" s="12">
+        <v>0.9</v>
+      </c>
+      <c r="M11" s="12">
         <f t="shared" si="3"/>
-        <v>0.9</v>
-      </c>
-      <c r="M11" s="12">
-        <f t="shared" si="4"/>
         <v>0.01</v>
       </c>
       <c r="N11" s="12">
@@ -3071,7 +3085,7 @@
         <v>0.01</v>
       </c>
       <c r="O11" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0.01</v>
       </c>
       <c r="P11">
@@ -3079,7 +3093,7 @@
         <v>0.01</v>
       </c>
       <c r="Q11">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1710</v>
       </c>
       <c r="R11">
@@ -3107,22 +3121,22 @@
     </row>
     <row r="12" spans="1:26">
       <c r="A12" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E12">
         <v>50</v>
       </c>
       <c r="F12">
-        <v>2000</v>
+        <v>2</v>
       </c>
       <c r="G12">
         <v>0.3</v>
@@ -3131,24 +3145,24 @@
         <f t="array" ref="H12">_xlfn.IFS(ISBLANK(B12), "",C12="Sugar Cane", VLOOKUP(D12, $Y$48:$Z$50, 2, FALSE),_xlfn.IFNA(MATCH(C12, $X$43:$X$47, 0), FALSE), VLOOKUP(C12, $X$43:$Z$47, 3, FALSE), TRUE, VLOOKUP(D12, $Y$51:$Z$53, 2, FALSE))</f>
         <v>0</v>
       </c>
-      <c r="I12">
+      <c r="I12" s="12">
+        <f t="shared" si="6"/>
+        <v>100000</v>
+      </c>
+      <c r="J12" s="12">
         <f t="shared" si="0"/>
-        <v>100000</v>
-      </c>
-      <c r="J12" s="12">
+        <v>1.5</v>
+      </c>
+      <c r="K12" s="12">
         <f t="shared" si="1"/>
-        <v>1.5</v>
-      </c>
-      <c r="K12" s="12">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="L12" s="12">
         <f t="shared" si="2"/>
-        <v>0.28999999999999998</v>
-      </c>
-      <c r="L12" s="12">
+        <v>0.88</v>
+      </c>
+      <c r="M12" s="12">
         <f t="shared" si="3"/>
-        <v>0.88</v>
-      </c>
-      <c r="M12" s="12">
-        <f t="shared" si="4"/>
         <v>6.0000000000000001E-3</v>
       </c>
       <c r="N12" s="12">
@@ -3156,7 +3170,7 @@
         <v>6.0000000000000001E-3</v>
       </c>
       <c r="O12" s="12" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>n/a</v>
       </c>
       <c r="P12">
@@ -3164,7 +3178,7 @@
         <v>0</v>
       </c>
       <c r="Q12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>554.4</v>
       </c>
       <c r="R12">
@@ -3194,22 +3208,22 @@
     </row>
     <row r="13" spans="1:26">
       <c r="A13" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E13">
         <v>50</v>
       </c>
       <c r="F13">
-        <v>2000</v>
+        <v>2</v>
       </c>
       <c r="G13">
         <v>0.3</v>
@@ -3218,24 +3232,24 @@
         <f t="array" ref="H13">_xlfn.IFS(ISBLANK(B13), "",C13="Sugar Cane", VLOOKUP(D13, $Y$48:$Z$50, 2, FALSE),_xlfn.IFNA(MATCH(C13, $X$43:$X$47, 0), FALSE), VLOOKUP(C13, $X$43:$Z$47, 3, FALSE), TRUE, VLOOKUP(D13, $Y$51:$Z$53, 2, FALSE))</f>
         <v>0.8</v>
       </c>
-      <c r="I13">
+      <c r="I13" s="12">
+        <f t="shared" si="6"/>
+        <v>100000</v>
+      </c>
+      <c r="J13" s="12">
         <f t="shared" si="0"/>
-        <v>100000</v>
-      </c>
-      <c r="J13" s="12">
+        <v>1.34</v>
+      </c>
+      <c r="K13" s="12">
         <f t="shared" si="1"/>
-        <v>1.34</v>
-      </c>
-      <c r="K13" s="12">
+        <v>0.37</v>
+      </c>
+      <c r="L13" s="12">
         <f t="shared" si="2"/>
-        <v>0.37</v>
-      </c>
-      <c r="L13" s="12">
+        <v>0.88</v>
+      </c>
+      <c r="M13" s="12">
         <f t="shared" si="3"/>
-        <v>0.88</v>
-      </c>
-      <c r="M13" s="12">
-        <f t="shared" si="4"/>
         <v>6.0000000000000001E-3</v>
       </c>
       <c r="N13" s="12">
@@ -3243,7 +3257,7 @@
         <v>6.0000000000000001E-3</v>
       </c>
       <c r="O13" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0.01</v>
       </c>
       <c r="P13">
@@ -3251,7 +3265,7 @@
         <v>0.01</v>
       </c>
       <c r="Q13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>365.55199999999996</v>
       </c>
       <c r="R13">
@@ -3280,22 +3294,22 @@
     </row>
     <row r="14" spans="1:26">
       <c r="A14" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="D14" s="15" t="s">
-        <v>63</v>
+        <v>70</v>
+      </c>
+      <c r="D14" s="14" t="s">
+        <v>62</v>
       </c>
       <c r="E14">
         <v>50</v>
       </c>
       <c r="F14">
-        <v>2000</v>
+        <v>2</v>
       </c>
       <c r="G14">
         <v>0.3</v>
@@ -3304,24 +3318,24 @@
         <f t="array" ref="H14">_xlfn.IFS(ISBLANK(B14), "",C14="Sugar Cane", VLOOKUP(D14, $Y$48:$Z$50, 2, FALSE),_xlfn.IFNA(MATCH(C14, $X$43:$X$47, 0), FALSE), VLOOKUP(C14, $X$43:$Z$47, 3, FALSE), TRUE, VLOOKUP(D14, $Y$51:$Z$53, 2, FALSE))</f>
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="I14">
+      <c r="I14" s="12">
+        <f t="shared" si="6"/>
+        <v>100000</v>
+      </c>
+      <c r="J14" s="12">
         <f t="shared" si="0"/>
-        <v>100000</v>
-      </c>
-      <c r="J14" s="12">
+        <v>1.37</v>
+      </c>
+      <c r="K14" s="12">
         <f t="shared" si="1"/>
-        <v>1.37</v>
-      </c>
-      <c r="K14" s="12">
+        <v>0.51</v>
+      </c>
+      <c r="L14" s="12">
         <f t="shared" si="2"/>
-        <v>0.51</v>
-      </c>
-      <c r="L14" s="12">
+        <v>0.87</v>
+      </c>
+      <c r="M14" s="12">
         <f t="shared" si="3"/>
-        <v>0.87</v>
-      </c>
-      <c r="M14" s="12">
-        <f t="shared" si="4"/>
         <v>8.9999999999999993E-3</v>
       </c>
       <c r="N14" s="12">
@@ -3329,7 +3343,7 @@
         <v>8.9999999999999993E-3</v>
       </c>
       <c r="O14" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0.01</v>
       </c>
       <c r="P14">
@@ -3337,7 +3351,7 @@
         <v>0.01</v>
       </c>
       <c r="Q14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1283.6762999999999</v>
       </c>
       <c r="R14">
@@ -3373,7 +3387,7 @@
     <row r="15" spans="1:26">
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
-      <c r="D15" s="15"/>
+      <c r="D15" s="14"/>
       <c r="J15" s="12"/>
       <c r="K15" s="12"/>
       <c r="L15" s="12"/>
@@ -3391,128 +3405,68 @@
       </c>
     </row>
     <row r="16" spans="1:26">
-      <c r="B16" s="16"/>
-      <c r="C16" s="16"/>
-      <c r="D16" s="17"/>
-      <c r="E16" s="13"/>
-      <c r="F16" s="13"/>
-      <c r="G16" s="13"/>
-      <c r="H16" s="13"/>
-      <c r="I16" s="13"/>
-      <c r="J16" s="18"/>
-      <c r="K16" s="18"/>
-      <c r="L16" s="18"/>
-      <c r="M16" s="18"/>
-      <c r="N16" s="18"/>
-      <c r="O16" s="18"/>
-      <c r="P16" s="13"/>
-      <c r="Q16" s="13"/>
-      <c r="R16" s="13"/>
-      <c r="S16" s="13"/>
-      <c r="T16" s="13"/>
-      <c r="U16" s="13"/>
-      <c r="V16" s="13"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="14"/>
+      <c r="J16" s="12"/>
+      <c r="K16" s="12"/>
+      <c r="L16" s="12"/>
+      <c r="M16" s="12"/>
+      <c r="N16" s="12"/>
+      <c r="O16" s="12"/>
       <c r="X16" s="2"/>
       <c r="Y16" s="2"/>
       <c r="Z16" s="8"/>
     </row>
     <row r="17" spans="2:32">
-      <c r="B17" s="16"/>
-      <c r="C17" s="16"/>
-      <c r="D17" s="17"/>
-      <c r="E17" s="13"/>
-      <c r="F17" s="13"/>
-      <c r="G17" s="13"/>
-      <c r="H17" s="13"/>
-      <c r="I17" s="13"/>
-      <c r="J17" s="18"/>
-      <c r="K17" s="18"/>
-      <c r="L17" s="18"/>
-      <c r="M17" s="18"/>
-      <c r="N17" s="18"/>
-      <c r="O17" s="18"/>
-      <c r="P17" s="13"/>
-      <c r="Q17" s="13"/>
-      <c r="R17" s="13"/>
-      <c r="S17" s="13"/>
-      <c r="T17" s="13"/>
-      <c r="U17" s="13"/>
-      <c r="V17" s="13"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="14"/>
+      <c r="J17" s="12"/>
+      <c r="K17" s="12"/>
+      <c r="L17" s="12"/>
+      <c r="M17" s="12"/>
+      <c r="N17" s="12"/>
+      <c r="O17" s="12"/>
     </row>
     <row r="18" spans="2:32">
-      <c r="B18" s="16"/>
-      <c r="C18" s="16"/>
-      <c r="D18" s="17"/>
-      <c r="E18" s="13"/>
-      <c r="F18" s="13"/>
-      <c r="G18" s="13"/>
-      <c r="H18" s="13"/>
-      <c r="I18" s="13"/>
-      <c r="J18" s="18"/>
-      <c r="K18" s="18"/>
-      <c r="L18" s="18"/>
-      <c r="M18" s="18"/>
-      <c r="N18" s="18"/>
-      <c r="O18" s="18"/>
-      <c r="P18" s="13"/>
-      <c r="Q18" s="13"/>
-      <c r="R18" s="13"/>
-      <c r="S18" s="13"/>
-      <c r="T18" s="13"/>
-      <c r="U18" s="13"/>
-      <c r="V18" s="13"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="14"/>
+      <c r="J18" s="12"/>
+      <c r="K18" s="12"/>
+      <c r="L18" s="12"/>
+      <c r="M18" s="12"/>
+      <c r="N18" s="12"/>
+      <c r="O18" s="12"/>
       <c r="X18" s="2"/>
       <c r="Y18" s="2"/>
     </row>
     <row r="19" spans="2:32">
-      <c r="B19" s="16"/>
-      <c r="C19" s="16"/>
-      <c r="D19" s="17"/>
-      <c r="E19" s="13"/>
-      <c r="F19" s="13"/>
-      <c r="G19" s="13"/>
-      <c r="H19" s="13"/>
-      <c r="I19" s="13"/>
-      <c r="J19" s="18"/>
-      <c r="K19" s="18"/>
-      <c r="L19" s="18"/>
-      <c r="M19" s="18"/>
-      <c r="N19" s="18"/>
-      <c r="O19" s="18"/>
-      <c r="P19" s="13"/>
-      <c r="Q19" s="13"/>
-      <c r="R19" s="13"/>
-      <c r="S19" s="13"/>
-      <c r="T19" s="13"/>
-      <c r="U19" s="13"/>
-      <c r="V19" s="13"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="14"/>
+      <c r="J19" s="12"/>
+      <c r="K19" s="12"/>
+      <c r="L19" s="12"/>
+      <c r="M19" s="12"/>
+      <c r="N19" s="12"/>
+      <c r="O19" s="12"/>
       <c r="X19" s="2"/>
       <c r="Y19" s="2"/>
     </row>
     <row r="20" spans="2:32">
-      <c r="B20" s="16"/>
-      <c r="C20" s="16"/>
-      <c r="D20" s="17"/>
-      <c r="E20" s="13"/>
-      <c r="F20" s="13"/>
-      <c r="G20" s="13"/>
-      <c r="H20" s="13"/>
-      <c r="I20" s="13"/>
-      <c r="J20" s="18"/>
-      <c r="K20" s="18"/>
-      <c r="L20" s="18"/>
-      <c r="M20" s="18"/>
-      <c r="N20" s="18"/>
-      <c r="O20" s="18"/>
-      <c r="P20" s="13"/>
-      <c r="Q20" s="13"/>
-      <c r="R20" s="13"/>
-      <c r="S20" s="13"/>
-      <c r="T20" s="13"/>
-      <c r="U20" s="13"/>
-      <c r="V20" s="13"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="14"/>
+      <c r="J20" s="12"/>
+      <c r="K20" s="12"/>
+      <c r="L20" s="12"/>
+      <c r="M20" s="12"/>
+      <c r="N20" s="12"/>
+      <c r="O20" s="12"/>
       <c r="X20" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="Y20" s="2"/>
       <c r="AB20" s="7"/>
@@ -3521,34 +3475,34 @@
       <c r="B21" s="3"/>
       <c r="X21" s="2"/>
       <c r="Y21" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z21" t="s">
         <v>53</v>
       </c>
-      <c r="Z21" t="s">
+      <c r="AA21" t="s">
         <v>54</v>
       </c>
-      <c r="AA21" t="s">
+      <c r="AB21" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="AC21" t="s">
         <v>55</v>
       </c>
-      <c r="AB21" s="7" t="s">
+      <c r="AD21" t="s">
         <v>93</v>
       </c>
-      <c r="AC21" t="s">
-        <v>56</v>
-      </c>
-      <c r="AD21" t="s">
+      <c r="AE21" t="s">
         <v>94</v>
       </c>
-      <c r="AE21" t="s">
+      <c r="AF21" t="s">
         <v>95</v>
-      </c>
-      <c r="AF21" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="22" spans="2:32">
       <c r="B22" s="3"/>
       <c r="X22" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="Y22" s="11">
         <v>1.5</v>
@@ -3581,7 +3535,7 @@
       <c r="D23" s="2"/>
       <c r="O23" s="12"/>
       <c r="X23" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="Y23" s="11">
         <v>1.24</v>
@@ -3613,7 +3567,7 @@
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
       <c r="X24" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Y24" s="11">
         <v>0.81</v>
@@ -3647,7 +3601,7 @@
         <v/>
       </c>
       <c r="X25" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="Y25" s="11">
         <v>1.42</v>
@@ -3681,7 +3635,7 @@
         <v/>
       </c>
       <c r="X26" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="Y26" s="11">
         <v>1.31</v>
@@ -3715,7 +3669,7 @@
         <v/>
       </c>
       <c r="X27" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Y27" s="11">
         <v>1.5</v>
@@ -3749,7 +3703,7 @@
         <v/>
       </c>
       <c r="X28" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Y28" s="11">
         <v>1.5</v>
@@ -3779,7 +3733,7 @@
     <row r="29" spans="2:32">
       <c r="B29" s="3"/>
       <c r="X29" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="Y29" s="11">
         <v>1.46</v>
@@ -3809,7 +3763,7 @@
     <row r="30" spans="2:32">
       <c r="B30" s="3"/>
       <c r="X30" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="Y30" s="11">
         <v>1.37</v>
@@ -3839,7 +3793,7 @@
     <row r="31" spans="2:32">
       <c r="B31" s="3"/>
       <c r="X31" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="Y31" s="11">
         <v>0.34</v>
@@ -3860,7 +3814,7 @@
         <v>0.01</v>
       </c>
       <c r="AE31" s="10" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AF31" s="10">
         <v>0.85</v>
@@ -3869,7 +3823,7 @@
     <row r="32" spans="2:32">
       <c r="B32" s="3"/>
       <c r="X32" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Y32" s="11">
         <v>1.07</v>
@@ -3899,7 +3853,7 @@
     <row r="33" spans="2:32">
       <c r="B33" s="3"/>
       <c r="X33" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Y33" s="11">
         <v>0.25</v>
@@ -3929,7 +3883,7 @@
     <row r="34" spans="2:32">
       <c r="B34" s="3"/>
       <c r="X34" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="Y34" s="11">
         <v>1.9</v>
@@ -3950,7 +3904,7 @@
         <v>0.01</v>
       </c>
       <c r="AE34" s="10" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AF34" s="10">
         <v>0.85</v>
@@ -3959,7 +3913,7 @@
     <row r="35" spans="2:32">
       <c r="B35" s="3"/>
       <c r="X35" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="Y35" s="11">
         <v>1.5</v>
@@ -3977,10 +3931,10 @@
         <v>6.0000000000000001E-3</v>
       </c>
       <c r="AD35" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="AE35" s="10" t="s">
         <v>97</v>
-      </c>
-      <c r="AE35" s="10" t="s">
-        <v>98</v>
       </c>
       <c r="AF35" s="10">
         <v>0.85</v>
@@ -3989,7 +3943,7 @@
     <row r="36" spans="2:32">
       <c r="B36" s="3"/>
       <c r="X36" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Y36" s="11">
         <v>2.08</v>
@@ -4019,7 +3973,7 @@
     <row r="37" spans="2:32">
       <c r="B37" s="3"/>
       <c r="X37" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="Y37" s="11">
         <v>1.34</v>
@@ -4040,7 +3994,7 @@
         <v>0.01</v>
       </c>
       <c r="AE37" s="10" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AF37" s="10">
         <v>0.85</v>
@@ -4049,7 +4003,7 @@
     <row r="38" spans="2:32">
       <c r="B38" s="3"/>
       <c r="X38" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="Y38" s="9">
         <v>1</v>
@@ -4070,16 +4024,16 @@
         <v>8.9999999999999993E-3</v>
       </c>
       <c r="AE38" s="9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AF38" s="9" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="39" spans="2:32">
       <c r="B39" s="3"/>
       <c r="X39" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="Y39" s="9">
         <v>1.5</v>
@@ -4097,13 +4051,13 @@
         <v>6.0000000000000001E-3</v>
       </c>
       <c r="AD39" s="9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AE39" s="9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AF39" s="9" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="40" spans="2:32">
@@ -4120,22 +4074,22 @@
     <row r="42" spans="2:32">
       <c r="B42" s="3"/>
       <c r="X42" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="Y42" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="Z42" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="43" spans="2:32">
       <c r="B43" s="3"/>
       <c r="X43" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="Y43" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="Z43">
         <v>0.06</v>
@@ -4144,10 +4098,10 @@
     <row r="44" spans="2:32">
       <c r="B44" s="3"/>
       <c r="X44" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="Y44" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="Z44">
         <v>1</v>
@@ -4156,10 +4110,10 @@
     <row r="45" spans="2:32">
       <c r="B45" s="3"/>
       <c r="X45" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="Y45" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -4168,10 +4122,10 @@
     <row r="46" spans="2:32">
       <c r="B46" s="3"/>
       <c r="X46" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="Y46" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -4180,10 +4134,10 @@
     <row r="47" spans="2:32">
       <c r="B47" s="3"/>
       <c r="X47" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="Y47" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="Z47">
         <v>0.8</v>
@@ -4192,10 +4146,10 @@
     <row r="48" spans="2:32">
       <c r="B48" s="3"/>
       <c r="X48" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="Y48" s="2" t="s">
         <v>60</v>
-      </c>
-      <c r="Y48" s="2" t="s">
-        <v>61</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -4204,10 +4158,10 @@
     <row r="49" spans="2:26">
       <c r="B49" s="3"/>
       <c r="X49" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="Y49" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="Z49">
         <v>0.03</v>
@@ -4216,10 +4170,10 @@
     <row r="50" spans="2:26">
       <c r="B50" s="3"/>
       <c r="X50" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="Y50" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -4228,10 +4182,10 @@
     <row r="51" spans="2:26">
       <c r="B51" s="3"/>
       <c r="X51" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="Y51" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="Z51">
         <v>0.05</v>
@@ -4240,10 +4194,10 @@
     <row r="52" spans="2:26">
       <c r="B52" s="3"/>
       <c r="X52" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="Y52" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Z52">
         <v>7.0000000000000007E-2</v>
@@ -4252,10 +4206,10 @@
     <row r="53" spans="2:26">
       <c r="B53" s="3"/>
       <c r="X53" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="Y53" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="Z53">
         <v>0.04</v>
@@ -4264,10 +4218,10 @@
     <row r="54" spans="2:26">
       <c r="B54" s="3"/>
       <c r="X54" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="Y54" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="Z54">
         <v>0.09</v>
@@ -4276,10 +4230,10 @@
     <row r="55" spans="2:26">
       <c r="B55" s="3"/>
       <c r="X55" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="Y55" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="Z55">
         <v>0.11</v>
@@ -4288,10 +4242,10 @@
     <row r="56" spans="2:26">
       <c r="B56" s="3"/>
       <c r="X56" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="Y56" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Z56">
         <v>0.16</v>
@@ -4300,10 +4254,10 @@
     <row r="57" spans="2:26">
       <c r="B57" s="3"/>
       <c r="X57" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="Y57" s="2" t="s">
         <v>90</v>
-      </c>
-      <c r="Y57" s="2" t="s">
-        <v>91</v>
       </c>
       <c r="Z57">
         <v>0.01</v>
@@ -4312,10 +4266,10 @@
     <row r="58" spans="2:26">
       <c r="B58" s="3"/>
       <c r="X58" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="Y58" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="Z58">
         <v>0</v>
